--- a/excel/piece_count_distribution_10k.xlsx
+++ b/excel/piece_count_distribution_10k.xlsx
@@ -433,7 +433,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +441,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>2116</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="4">
@@ -449,7 +449,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3763</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +457,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>4184</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="6">
@@ -465,7 +465,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>5037</v>
+        <v>5329</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>6295</v>
+        <v>6601</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>7940</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +489,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>8653</v>
+        <v>9114</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +497,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>9228</v>
+        <v>9701</v>
       </c>
     </row>
     <row r="11">
@@ -505,7 +505,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>10617</v>
+        <v>11197</v>
       </c>
     </row>
     <row r="12">
@@ -513,7 +513,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>11482</v>
+        <v>12177</v>
       </c>
     </row>
     <row r="13">
@@ -521,7 +521,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>12428</v>
+        <v>13133</v>
       </c>
     </row>
     <row r="14">
@@ -529,7 +529,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>13472</v>
+        <v>14366</v>
       </c>
     </row>
     <row r="15">
@@ -537,7 +537,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>14009</v>
+        <v>14842</v>
       </c>
     </row>
     <row r="16">
@@ -545,7 +545,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="n">
-        <v>15409</v>
+        <v>16335</v>
       </c>
     </row>
     <row r="17">
@@ -553,7 +553,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="n">
-        <v>16242</v>
+        <v>17201</v>
       </c>
     </row>
     <row r="18">
@@ -561,7 +561,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="n">
-        <v>17373</v>
+        <v>18527</v>
       </c>
     </row>
     <row r="19">
@@ -569,7 +569,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="n">
-        <v>17900</v>
+        <v>19111</v>
       </c>
     </row>
     <row r="20">
@@ -577,7 +577,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="n">
-        <v>19620</v>
+        <v>20977</v>
       </c>
     </row>
     <row r="21">
@@ -585,7 +585,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="n">
-        <v>20214</v>
+        <v>21590</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="n">
-        <v>22566</v>
+        <v>24113</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +601,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="n">
-        <v>21235</v>
+        <v>22696</v>
       </c>
     </row>
     <row r="24">
@@ -609,7 +609,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="n">
-        <v>26420</v>
+        <v>28024</v>
       </c>
     </row>
     <row r="25">
@@ -617,7 +617,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="n">
-        <v>23039</v>
+        <v>24462</v>
       </c>
     </row>
     <row r="26">
@@ -625,7 +625,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="n">
-        <v>29943</v>
+        <v>32046</v>
       </c>
     </row>
     <row r="27">
@@ -633,7 +633,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="n">
-        <v>22737</v>
+        <v>24067</v>
       </c>
     </row>
     <row r="28">
@@ -641,7 +641,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="n">
-        <v>37152</v>
+        <v>39613</v>
       </c>
     </row>
     <row r="29">
@@ -649,7 +649,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="n">
-        <v>20759</v>
+        <v>21806</v>
       </c>
     </row>
     <row r="30">
@@ -657,7 +657,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="n">
-        <v>51492</v>
+        <v>53997</v>
       </c>
     </row>
     <row r="31">
@@ -665,7 +665,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="n">
-        <v>18368</v>
+        <v>18750</v>
       </c>
     </row>
     <row r="32">
@@ -673,7 +673,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="n">
-        <v>109645</v>
+        <v>112472</v>
       </c>
     </row>
   </sheetData>
